--- a/resource/part list.xlsx
+++ b/resource/part list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoe\Meng\pressure-sensing-cushion\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC0745E-F29F-49AD-B9B4-77FDC2A39D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A083B1F-048B-4520-877B-942E1BBADC95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{039EFAA4-C4D2-4F31-ABF8-5ECCF156DD30}"/>
   </bookViews>
@@ -43,7 +43,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="3">
+  <futureMetadata name="XLRICHVALUE" count="4">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -65,8 +65,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="3">
+  <valueMetadata count="4">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -76,12 +83,15 @@
     <bk>
       <rc t="1" v="2"/>
     </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Quantity</t>
   </si>
@@ -129,6 +139,15 @@
   </si>
   <si>
     <t>Base / weight distributer</t>
+  </si>
+  <si>
+    <t>Resistor</t>
+  </si>
+  <si>
+    <t>10kOhm
+100kOhm
+4.7kOhm
+1kOhm</t>
   </si>
 </sst>
 </file>
@@ -192,7 +211,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -212,6 +231,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -272,7 +294,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -283,6 +305,10 @@
   </rv>
   <rv s="0">
     <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -302,6 +328,7 @@
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
   <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
 </richValueRels>
 </file>
 
@@ -715,7 +742,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="370.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:9" ht="320.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="6" spans="1:9" ht="195" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:9" ht="195" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:9" ht="194.25" customHeight="1" x14ac:dyDescent="0.3"/>
